--- a/data/parametrage_examens.xlsx
+++ b/data/parametrage_examens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AU 2026_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8FDC96-9F36-4DFB-A5A9-F88BD1CF64C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB1D434-221B-4110-A2A4-239BA37955B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" activeTab="2" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
+    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
   </bookViews>
   <sheets>
     <sheet name="matieres" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="49">
   <si>
     <t>L1</t>
   </si>
@@ -135,13 +135,52 @@
   </si>
   <si>
     <t>heureFin</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>LISI 2</t>
+  </si>
+  <si>
+    <t>LIGE 2</t>
+  </si>
+  <si>
+    <t>ALGEBRE 2</t>
+  </si>
+  <si>
+    <t>ANALYSE 2</t>
+  </si>
+  <si>
+    <t>MECANIQUE 2</t>
+  </si>
+  <si>
+    <t>SVT</t>
+  </si>
+  <si>
+    <t>MACHINES</t>
+  </si>
+  <si>
+    <t>SOLAIRES</t>
+  </si>
+  <si>
+    <t>CHIMIE 2</t>
+  </si>
+  <si>
+    <t>ADSL</t>
+  </si>
+  <si>
+    <t>ENERGIE</t>
+  </si>
+  <si>
+    <t>MATHS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +192,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -506,7 +551,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{674A9EC1-A3BA-4B0E-ABD7-BE4F7011DFD0}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" customWidth="1"/>
@@ -617,8 +662,248 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:6" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/data/parametrage_examens.xlsx
+++ b/data/parametrage_examens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AU 2026_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB1D434-221B-4110-A2A4-239BA37955B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD6406-62EE-46CD-8972-B184295BA4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
+    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" activeTab="2" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
   </bookViews>
   <sheets>
     <sheet name="matieres" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="49">
   <si>
     <t>L1</t>
   </si>
@@ -730,7 +730,7 @@
         <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>41</v>
@@ -1089,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB0BE12D-432C-4A85-8074-C62CD37633FF}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="25.28515625" customWidth="1"/>
@@ -1207,6 +1207,104 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.52083333333333337</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/parametrage_examens.xlsx
+++ b/data/parametrage_examens.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AU 2026_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CFD6406-62EE-46CD-8972-B184295BA4B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7F32BF-D377-46F8-B3A6-DCF7BE73C3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" activeTab="2" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
+    <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
   </bookViews>
   <sheets>
     <sheet name="matieres" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="48">
   <si>
     <t>L1</t>
   </si>
@@ -171,9 +171,6 @@
   </si>
   <si>
     <t>ENERGIE</t>
-  </si>
-  <si>
-    <t>MATHS</t>
   </si>
 </sst>
 </file>
@@ -883,24 +880,12 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1084,6 +1069,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1109,7 +1095,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>21</v>
       </c>
@@ -1123,7 +1109,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>21</v>
       </c>
@@ -1137,7 +1123,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -1151,7 +1137,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1165,7 +1151,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
@@ -1179,7 +1165,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
@@ -1193,7 +1179,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -1207,7 +1193,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1221,7 +1207,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1235,7 +1221,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1249,7 +1235,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
@@ -1263,7 +1249,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>29</v>
       </c>
@@ -1277,7 +1263,7 @@
         <v>0.52083333333333337</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>31</v>
       </c>
@@ -1291,7 +1277,7 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>31</v>
       </c>

--- a/data/parametrage_examens.xlsx
+++ b/data/parametrage_examens.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AU 2026_2027\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7F32BF-D377-46F8-B3A6-DCF7BE73C3D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3EC1B54-9AB0-4361-BDC0-B072FB4F153D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="525" yWindow="105" windowWidth="28275" windowHeight="15495" xr2:uid="{535A826E-5190-4251-9069-3D14DED28CAA}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="49">
   <si>
     <t>L1</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>ENERGIE</t>
+  </si>
+  <si>
+    <t>MATHS</t>
   </si>
 </sst>
 </file>
@@ -880,12 +883,24 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
